--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680803</v>
+        <v>121680805</v>
       </c>
       <c r="B2" t="n">
-        <v>92039</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578841</v>
+        <v>578769</v>
       </c>
       <c r="R2" t="n">
-        <v>6651677</v>
+        <v>6651850</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680671</v>
+        <v>121680746</v>
       </c>
       <c r="B3" t="n">
-        <v>56604</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102118</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579204</v>
+        <v>579090</v>
       </c>
       <c r="R3" t="n">
-        <v>6651216</v>
+        <v>6651557</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121682908</v>
+        <v>121680802</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,35 +937,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578730</v>
+        <v>578842</v>
       </c>
       <c r="R4" t="n">
-        <v>6651775</v>
+        <v>6651675</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121680746</v>
+        <v>121682908</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,50 +1062,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Hundsjön, Vstm</t>
+          <t>Myggsjön, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579090</v>
+        <v>578730</v>
       </c>
       <c r="R5" t="n">
-        <v>6651557</v>
+        <v>6651775</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1129,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121680805</v>
+        <v>121680671</v>
       </c>
       <c r="B6" t="n">
-        <v>92004</v>
+        <v>56604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,43 +1191,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>102118</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Myggsjön, Vstm</t>
+          <t>Lilla Hundsjön, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578769</v>
+        <v>579204</v>
       </c>
       <c r="R6" t="n">
-        <v>6651850</v>
+        <v>6651216</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1254,22 +1254,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121680802</v>
+        <v>121680803</v>
       </c>
       <c r="B7" t="n">
-        <v>92004</v>
+        <v>92039</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,30 +1312,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578842</v>
+        <v>578841</v>
       </c>
       <c r="R7" t="n">
-        <v>6651675</v>
+        <v>6651677</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680805</v>
+        <v>121682908</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578769</v>
+        <v>578730</v>
       </c>
       <c r="R2" t="n">
-        <v>6651850</v>
+        <v>6651775</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680746</v>
+        <v>121680671</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>56604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102118</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579090</v>
+        <v>579204</v>
       </c>
       <c r="R3" t="n">
-        <v>6651557</v>
+        <v>6651216</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121682908</v>
+        <v>121680746</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,50 +1062,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Myggsjön, Vstm</t>
+          <t>Lilla Hundsjön, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578730</v>
+        <v>579090</v>
       </c>
       <c r="R5" t="n">
-        <v>6651775</v>
+        <v>6651557</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1129,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121680671</v>
+        <v>121680803</v>
       </c>
       <c r="B6" t="n">
-        <v>56604</v>
+        <v>92039</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,25 +1187,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102118</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1213,21 +1213,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Hundsjön, Vstm</t>
+          <t>Myggsjön, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579204</v>
+        <v>578841</v>
       </c>
       <c r="R6" t="n">
-        <v>6651216</v>
+        <v>6651677</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1254,22 +1254,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121680803</v>
+        <v>121680805</v>
       </c>
       <c r="B7" t="n">
-        <v>92039</v>
+        <v>92004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,30 +1312,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578841</v>
+        <v>578769</v>
       </c>
       <c r="R7" t="n">
-        <v>6651677</v>
+        <v>6651850</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121682908</v>
+        <v>121680805</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578730</v>
+        <v>578769</v>
       </c>
       <c r="R2" t="n">
-        <v>6651775</v>
+        <v>6651850</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680802</v>
+        <v>121680803</v>
       </c>
       <c r="B4" t="n">
-        <v>92004</v>
+        <v>92039</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,30 +937,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578842</v>
+        <v>578841</v>
       </c>
       <c r="R4" t="n">
-        <v>6651675</v>
+        <v>6651677</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121680803</v>
+        <v>121682908</v>
       </c>
       <c r="B6" t="n">
-        <v>92039</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1213,9 +1213,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578841</v>
+        <v>578730</v>
       </c>
       <c r="R6" t="n">
-        <v>6651677</v>
+        <v>6651775</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,22 +1254,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121680805</v>
+        <v>121680802</v>
       </c>
       <c r="B7" t="n">
         <v>92004</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578769</v>
+        <v>578842</v>
       </c>
       <c r="R7" t="n">
-        <v>6651850</v>
+        <v>6651675</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680803</v>
+        <v>121680746</v>
       </c>
       <c r="B4" t="n">
-        <v>92039</v>
+        <v>56569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,47 +937,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Myggsjön, Vstm</t>
+          <t>Lilla Hundsjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578841</v>
+        <v>579090</v>
       </c>
       <c r="R4" t="n">
-        <v>6651677</v>
+        <v>6651557</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121680746</v>
+        <v>121680802</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
+        <v>92004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,46 +1066,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Hundsjön, Vstm</t>
+          <t>Myggsjön, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579090</v>
+        <v>578842</v>
       </c>
       <c r="R5" t="n">
-        <v>6651557</v>
+        <v>6651675</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1129,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121682908</v>
+        <v>121680803</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>92039</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1213,9 +1213,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578730</v>
+        <v>578841</v>
       </c>
       <c r="R6" t="n">
-        <v>6651775</v>
+        <v>6651677</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,22 +1254,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121680802</v>
+        <v>121682908</v>
       </c>
       <c r="B7" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,35 +1312,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578842</v>
+        <v>578730</v>
       </c>
       <c r="R7" t="n">
-        <v>6651675</v>
+        <v>6651775</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,22 +1379,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680805</v>
+        <v>121680802</v>
       </c>
       <c r="B2" t="n">
         <v>92004</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578769</v>
+        <v>578842</v>
       </c>
       <c r="R2" t="n">
-        <v>6651850</v>
+        <v>6651675</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680671</v>
+        <v>121680746</v>
       </c>
       <c r="B3" t="n">
-        <v>56604</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102118</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579204</v>
+        <v>579090</v>
       </c>
       <c r="R3" t="n">
-        <v>6651216</v>
+        <v>6651557</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680746</v>
+        <v>121680803</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>92039</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,47 +937,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Hundsjön, Vstm</t>
+          <t>Myggsjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579090</v>
+        <v>578841</v>
       </c>
       <c r="R4" t="n">
-        <v>6651557</v>
+        <v>6651677</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121680802</v>
+        <v>121680805</v>
       </c>
       <c r="B5" t="n">
         <v>92004</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578842</v>
+        <v>578769</v>
       </c>
       <c r="R5" t="n">
-        <v>6651675</v>
+        <v>6651850</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121680803</v>
+        <v>121680671</v>
       </c>
       <c r="B6" t="n">
-        <v>92039</v>
+        <v>56604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,25 +1187,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>102118</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1213,21 +1213,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Myggsjön, Vstm</t>
+          <t>Lilla Hundsjön, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578841</v>
+        <v>579204</v>
       </c>
       <c r="R6" t="n">
-        <v>6651677</v>
+        <v>6651216</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1254,22 +1254,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680802</v>
+        <v>121682908</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578842</v>
+        <v>578730</v>
       </c>
       <c r="R2" t="n">
-        <v>6651675</v>
+        <v>6651775</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680746</v>
+        <v>121680802</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,46 +816,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Hundsjön, Vstm</t>
+          <t>Myggsjön, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579090</v>
+        <v>578842</v>
       </c>
       <c r="R3" t="n">
-        <v>6651557</v>
+        <v>6651675</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1300,62 +1300,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121682908</v>
+        <v>121680746</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
+        <v>56569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Myggsjön, Vstm</t>
+          <t>Lilla Hundsjön, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578730</v>
+        <v>579090</v>
       </c>
       <c r="R7" t="n">
-        <v>6651775</v>
+        <v>6651557</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,22 +1379,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121682908</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680802</v>
+        <v>121680805</v>
       </c>
       <c r="B3" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578842</v>
+        <v>578769</v>
       </c>
       <c r="R3" t="n">
-        <v>6651675</v>
+        <v>6651850</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
         <v>121680803</v>
       </c>
       <c r="B4" t="n">
-        <v>92039</v>
+        <v>92053</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121680805</v>
+        <v>121680802</v>
       </c>
       <c r="B5" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578769</v>
+        <v>578842</v>
       </c>
       <c r="R5" t="n">
-        <v>6651850</v>
+        <v>6651675</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121680671</v>
+        <v>121680746</v>
       </c>
       <c r="B6" t="n">
-        <v>56604</v>
+        <v>56577</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102118</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579204</v>
+        <v>579090</v>
       </c>
       <c r="R6" t="n">
-        <v>6651216</v>
+        <v>6651557</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121680746</v>
+        <v>121680671</v>
       </c>
       <c r="B7" t="n">
-        <v>56569</v>
+        <v>56612</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>102118</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579090</v>
+        <v>579204</v>
       </c>
       <c r="R7" t="n">
-        <v>6651557</v>
+        <v>6651216</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121682908</v>
+        <v>121680803</v>
       </c>
       <c r="B2" t="n">
-        <v>57518</v>
+        <v>92055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578730</v>
+        <v>578841</v>
       </c>
       <c r="R2" t="n">
-        <v>6651775</v>
+        <v>6651677</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680805</v>
+        <v>121682908</v>
       </c>
       <c r="B3" t="n">
-        <v>92018</v>
+        <v>57518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,35 +812,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578769</v>
+        <v>578730</v>
       </c>
       <c r="R3" t="n">
-        <v>6651850</v>
+        <v>6651775</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680803</v>
+        <v>121680805</v>
       </c>
       <c r="B4" t="n">
-        <v>92053</v>
+        <v>92020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,30 +937,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578841</v>
+        <v>578769</v>
       </c>
       <c r="R4" t="n">
-        <v>6651677</v>
+        <v>6651850</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1053,7 @@
         <v>121680802</v>
       </c>
       <c r="B5" t="n">
-        <v>92018</v>
+        <v>92020</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121680746</v>
+        <v>121680671</v>
       </c>
       <c r="B6" t="n">
-        <v>56577</v>
+        <v>56612</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>102118</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579090</v>
+        <v>579204</v>
       </c>
       <c r="R6" t="n">
-        <v>6651557</v>
+        <v>6651216</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121680671</v>
+        <v>121680746</v>
       </c>
       <c r="B7" t="n">
-        <v>56612</v>
+        <v>56577</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102118</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579204</v>
+        <v>579090</v>
       </c>
       <c r="R7" t="n">
-        <v>6651216</v>
+        <v>6651557</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121680803</v>
       </c>
       <c r="B2" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121682908</v>
+        <v>121680805</v>
       </c>
       <c r="B3" t="n">
-        <v>57518</v>
+        <v>92021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,35 +812,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578730</v>
+        <v>578769</v>
       </c>
       <c r="R3" t="n">
-        <v>6651775</v>
+        <v>6651850</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680805</v>
+        <v>121680802</v>
       </c>
       <c r="B4" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578769</v>
+        <v>578842</v>
       </c>
       <c r="R4" t="n">
-        <v>6651850</v>
+        <v>6651675</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121680802</v>
+        <v>121682908</v>
       </c>
       <c r="B5" t="n">
-        <v>92020</v>
+        <v>57518</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,35 +1062,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578842</v>
+        <v>578730</v>
       </c>
       <c r="R5" t="n">
-        <v>6651675</v>
+        <v>6651775</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1129,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -1050,37 +1050,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121682908</v>
+        <v>121680671</v>
       </c>
       <c r="B5" t="n">
-        <v>57518</v>
+        <v>56612</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1095,17 +1095,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Myggsjön, Vstm</t>
+          <t>Lilla Hundsjön, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578730</v>
+        <v>579204</v>
       </c>
       <c r="R5" t="n">
-        <v>6651775</v>
+        <v>6651216</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1129,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121680671</v>
+        <v>121680746</v>
       </c>
       <c r="B6" t="n">
-        <v>56612</v>
+        <v>56577</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102118</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579204</v>
+        <v>579090</v>
       </c>
       <c r="R6" t="n">
-        <v>6651216</v>
+        <v>6651557</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121680746</v>
+        <v>121682908</v>
       </c>
       <c r="B7" t="n">
-        <v>56577</v>
+        <v>57518</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,50 +1312,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Hundsjön, Vstm</t>
+          <t>Myggsjön, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579090</v>
+        <v>578730</v>
       </c>
       <c r="R7" t="n">
-        <v>6651557</v>
+        <v>6651775</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,22 +1379,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680803</v>
+        <v>121680805</v>
       </c>
       <c r="B2" t="n">
-        <v>92056</v>
+        <v>92030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578841</v>
+        <v>578769</v>
       </c>
       <c r="R2" t="n">
-        <v>6651677</v>
+        <v>6651850</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680805</v>
+        <v>121680803</v>
       </c>
       <c r="B3" t="n">
-        <v>92021</v>
+        <v>92065</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,30 +812,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578769</v>
+        <v>578841</v>
       </c>
       <c r="R3" t="n">
-        <v>6651850</v>
+        <v>6651677</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
         <v>121680802</v>
       </c>
       <c r="B4" t="n">
-        <v>92021</v>
+        <v>92030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121680671</v>
+        <v>121680746</v>
       </c>
       <c r="B5" t="n">
-        <v>56612</v>
+        <v>56581</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102118</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579204</v>
+        <v>579090</v>
       </c>
       <c r="R5" t="n">
-        <v>6651216</v>
+        <v>6651557</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121680746</v>
+        <v>121680671</v>
       </c>
       <c r="B6" t="n">
-        <v>56577</v>
+        <v>56616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>102118</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579090</v>
+        <v>579204</v>
       </c>
       <c r="R6" t="n">
-        <v>6651557</v>
+        <v>6651216</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,7 +1303,7 @@
         <v>121682908</v>
       </c>
       <c r="B7" t="n">
-        <v>57518</v>
+        <v>57522</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>121680746</v>
       </c>
       <c r="B5" t="n">
-        <v>56581</v>
+        <v>56582</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>121680671</v>
       </c>
       <c r="B6" t="n">
-        <v>56616</v>
+        <v>56617</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>121682908</v>
       </c>
       <c r="B7" t="n">
-        <v>57522</v>
+        <v>57525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>121680746</v>
       </c>
       <c r="B5" t="n">
-        <v>56582</v>
+        <v>56584</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>121680671</v>
       </c>
       <c r="B6" t="n">
-        <v>56617</v>
+        <v>56619</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>121682908</v>
       </c>
       <c r="B7" t="n">
-        <v>57525</v>
+        <v>57527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121680746</v>
+        <v>121680671</v>
       </c>
       <c r="B5" t="n">
-        <v>56584</v>
+        <v>56619</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>102118</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579090</v>
+        <v>579204</v>
       </c>
       <c r="R5" t="n">
-        <v>6651557</v>
+        <v>6651216</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121680671</v>
+        <v>121680746</v>
       </c>
       <c r="B6" t="n">
-        <v>56619</v>
+        <v>56584</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102118</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579204</v>
+        <v>579090</v>
       </c>
       <c r="R6" t="n">
-        <v>6651216</v>
+        <v>6651557</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>121680671</v>
       </c>
       <c r="B5" t="n">
-        <v>56619</v>
+        <v>56624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>121680746</v>
       </c>
       <c r="B6" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>121682908</v>
       </c>
       <c r="B7" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -1318,11 +1318,6 @@
       <c r="E7" t="n">
         <v>103021</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 13993-2021 artfynd.xlsx
+++ b/artfynd/A 13993-2021 artfynd.xlsx
@@ -1303,7 +1303,7 @@
         <v>121682908</v>
       </c>
       <c r="B7" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,6 +1317,11 @@
       </c>
       <c r="E7" t="n">
         <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
